--- a/files/R01-R69全节点业务验收测试包/V00_R01-R69覆盖验证/V00_V00-SOURCE-DIFF-001_TEST-V00-003_资料来源与差异台账.xlsx
+++ b/files/R01-R69全节点业务验收测试包/V00_R01-R69覆盖验证/V00_V00-SOURCE-DIFF-001_TEST-V00-003_资料来源与差异台账.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源差异" sheetId="1" r:id="R546d252aa05b4b1a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源差异" sheetId="1" r:id="Rc692ce90b3494f7a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -42,7 +42,7 @@
       <x:name val="Arial Unicode MS"/>
     </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -59,8 +59,13 @@
         <x:fgColor rgb="FFFCE8E6"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF3F1"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="9">
+  <x:borders count="17">
     <x:border/>
     <x:border>
       <x:left/>
@@ -89,12 +94,64 @@
     <x:border>
       <x:right/>
       <x:bottom/>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:top style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:left>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:right>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:left>
+      <x:bottom style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:bottom style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:right>
+      <x:bottom style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:bottom>
     </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="41">
+  <x:cellXfs count="69">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -186,6 +243,70 @@
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -216,6 +337,38 @@
     </x:dxf>
   </x:dxfs>
 </x:styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2190750" cy="876300"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="0634cdbe-0d3a-4861-9c37-a9e7be80616d"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R565ade5825b94e2c"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -414,9 +567,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="16.219999313354492" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="12" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="11.109999656677246" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="34" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="28.780000686645508" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="25.559999465942383" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="18" hidden="0" customHeight="1">
@@ -426,14 +580,16 @@
       <x:c r="B1" s="4"/>
       <x:c r="C1" s="4"/>
       <x:c r="D1" s="4"/>
-    </x:row>
-    <x:row r="2" ht="21.600000381469727" hidden="0" customHeight="1">
+      <x:c r="E1" s="4"/>
+    </x:row>
+    <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="9" t="str">
         <x:v>测试专用／合成资料／不得用于真实工程｜TEST-ONLY / SYNTHETIC / NOT FOR REAL ENGINEERING USE｜文件编号：TEST-V00-003｜版本：0｜日期：2026-07-15</x:v>
       </x:c>
       <x:c r="B2" s="9"/>
       <x:c r="C2" s="9"/>
       <x:c r="D2" s="9"/>
+      <x:c r="E2" s="9"/>
     </x:row>
     <x:row r="3"/>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
@@ -441,121 +597,143 @@
         <x:v>数据项</x:v>
       </x:c>
       <x:c r="B4" s="13" t="str">
-        <x:v>来源／设置</x:v>
+        <x:v>来源事实</x:v>
       </x:c>
       <x:c r="C4" s="13" t="str">
-        <x:v>使用方式</x:v>
+        <x:v>适用范围</x:v>
       </x:c>
       <x:c r="D4" s="13" t="str">
         <x:v>差异控制</x:v>
       </x:c>
-    </x:row>
-    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="E4" s="13" t="str">
+        <x:v>状态</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A5" s="32" t="str">
-        <x:v>项目名称</x:v>
+        <x:v>壁厚</x:v>
       </x:c>
       <x:c r="B5" s="33" t="str">
-        <x:v>既有施工图</x:v>
+        <x:v>施工图设计基线Φ108×4；2021交工与RT证据PL8303/PL8306为Φ108×5</x:v>
       </x:c>
       <x:c r="C5" s="33" t="str">
-        <x:v>原样复用</x:v>
-      </x:c>
-      <x:c r="D5" s="34" t="str">
-        <x:v>无差异</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="15" hidden="0" customHeight="1">
+        <x:v>设计值与实施值分栏使用</x:v>
+      </x:c>
+      <x:c r="D5" s="33" t="str">
+        <x:v>不静默覆盖；按对象和资料阶段追溯</x:v>
+      </x:c>
+      <x:c r="E5" s="34" t="str">
+        <x:v>已闭环</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A6" s="35" t="str">
-        <x:v>设计单位</x:v>
+        <x:v>介质</x:v>
       </x:c>
       <x:c r="B6" s="36" t="str">
-        <x:v>既有施工图</x:v>
+        <x:v>交工资料确认PL8303/PL8306为丙醇；设计扫描OCR存在丙酮/丙醇低置信差异</x:v>
       </x:c>
       <x:c r="C6" s="36" t="str">
-        <x:v>原样复用</x:v>
-      </x:c>
-      <x:c r="D6" s="37" t="str">
-        <x:v>无差异</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="15" hidden="0" customHeight="1">
+        <x:v>交工对象采用丙醇；设计OCR差异保留复核标记</x:v>
+      </x:c>
+      <x:c r="D6" s="36" t="str">
+        <x:v>不以低置信OCR替代原图</x:v>
+      </x:c>
+      <x:c r="E6" s="37" t="str">
+        <x:v>已闭环</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A7" s="35" t="str">
-        <x:v>图号</x:v>
+        <x:v>管线范围</x:v>
       </x:c>
       <x:c r="B7" s="36" t="str">
-        <x:v>QX201903S-13-Y-07、-10</x:v>
+        <x:v>施工图范围8条基础管线；交工原件主要覆盖PL8303和PL8306</x:v>
       </x:c>
       <x:c r="C7" s="36" t="str">
-        <x:v>基础事实</x:v>
-      </x:c>
-      <x:c r="D7" s="37" t="str">
-        <x:v>无差异</x:v>
+        <x:v>PL8303-100与PL8306-100作为交工别名</x:v>
+      </x:c>
+      <x:c r="D7" s="36" t="str">
+        <x:v>设计范围与交工证据范围分别统计</x:v>
+      </x:c>
+      <x:c r="E7" s="37" t="str">
+        <x:v>已闭环</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="35" t="str">
-        <x:v>原设计参数</x:v>
+        <x:v>无损检测单位</x:v>
       </x:c>
       <x:c r="B8" s="36" t="str">
-        <x:v>20#／Φ108×4／0.55 MPa</x:v>
+        <x:v>交工资料登记南京金鑫；具体RT报告由广州声华签发</x:v>
       </x:c>
       <x:c r="C8" s="36" t="str">
-        <x:v>B00保持</x:v>
-      </x:c>
-      <x:c r="D8" s="37" t="str">
-        <x:v>无差异</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="21.600000381469727" hidden="0" customHeight="1">
-      <x:c r="A9" s="35" t="str">
-        <x:v>新增单位人员</x:v>
-      </x:c>
-      <x:c r="B9" s="36" t="str">
-        <x:v>TEST前缀</x:v>
-      </x:c>
-      <x:c r="C9" s="36" t="str">
-        <x:v>测试身份</x:v>
-      </x:c>
-      <x:c r="D9" s="37" t="str">
-        <x:v>不得用于真实工程</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="15" hidden="0" customHeight="1">
-      <x:c r="A10" s="35" t="str">
-        <x:v>S01—S06</x:v>
-      </x:c>
-      <x:c r="B10" s="36" t="str">
-        <x:v>测试专用设计变更</x:v>
-      </x:c>
-      <x:c r="C10" s="36" t="str">
-        <x:v>独立场景</x:v>
-      </x:c>
-      <x:c r="D10" s="37" t="str">
-        <x:v>不污染基础资料</x:v>
-      </x:c>
-    </x:row>
+        <x:v>分别记录汇总登记角色和报告签发角色</x:v>
+      </x:c>
+      <x:c r="D8" s="36" t="str">
+        <x:v>两单位不合并、不互相替代</x:v>
+      </x:c>
+      <x:c r="E8" s="37" t="str">
+        <x:v>已闭环</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="38" t="str">
+        <x:v>证书时效</x:v>
+      </x:c>
+      <x:c r="B9" s="39" t="str">
+        <x:v>既有设计、施工、制造和焊工资质均为来源年份证据</x:v>
+      </x:c>
+      <x:c r="C9" s="39" t="str">
+        <x:v>只支撑2021来源事实</x:v>
+      </x:c>
+      <x:c r="D9" s="39" t="str">
+        <x:v>2026条件场景继续使用TEST前缀资质数据</x:v>
+      </x:c>
+      <x:c r="E9" s="40" t="str">
+        <x:v>已闭环</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10"/>
     <x:row r="11" ht="15" hidden="0" customHeight="1">
-      <x:c r="A11" s="38" t="str">
-        <x:v>施工照片</x:v>
-      </x:c>
-      <x:c r="B11" s="39" t="str">
-        <x:v>占位附件</x:v>
-      </x:c>
-      <x:c r="C11" s="39" t="str">
-        <x:v>存在性／可读性</x:v>
-      </x:c>
-      <x:c r="D11" s="40" t="str">
-        <x:v>未执行OCR</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12"/>
-    <x:row r="13"/>
+      <x:c r="A11" s="60" t="str">
+        <x:v>电子签署（测试）｜资料验收测试专用章</x:v>
+      </x:c>
+      <x:c r="B11" s="61"/>
+      <x:c r="C11" s="61"/>
+      <x:c r="D11" s="61"/>
+      <x:c r="E11" s="62"/>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12" s="63"/>
+      <x:c r="B12" s="64"/>
+      <x:c r="C12" s="64"/>
+      <x:c r="D12" s="64"/>
+      <x:c r="E12" s="65"/>
+    </x:row>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
+      <x:c r="A13" s="63"/>
+      <x:c r="B13" s="64"/>
+      <x:c r="C13" s="64"/>
+      <x:c r="D13" s="64"/>
+      <x:c r="E13" s="65"/>
+    </x:row>
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
+      <x:c r="A14" s="66"/>
+      <x:c r="B14" s="67"/>
+      <x:c r="C14" s="67"/>
+      <x:c r="D14" s="67"/>
+      <x:c r="E14" s="68"/>
+    </x:row>
+    <x:row r="15"/>
+    <x:row r="16"/>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:D1"/>
-    <x:mergeCell ref="A2:D2"/>
+    <x:mergeCell ref="A1:E1"/>
+    <x:mergeCell ref="A2:E2"/>
+    <x:mergeCell ref="A11:C11"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="A5:D11">
+  <x:conditionalFormatting sqref="A5:E9">
     <x:cfRule type="expression" dxfId="0" priority="1">
       <x:formula>OR(ISNUMBER(SEARCH("不合格",A5)),ISNUMBER(SEARCH("异常",A5)))</x:formula>
     </x:cfRule>
@@ -564,5 +742,6 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R05cb9f2aaae445d0"/>
 </x:worksheet>
 </file>